--- a/02_地图工程/建筑点位台账.xlsx
+++ b/02_地图工程/建筑点位台账.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -43,11 +43,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002E4053"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005DADE2"/>
       </patternFill>
     </fill>
     <fill>
@@ -62,22 +57,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="005DADE2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="007D6B91"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAD7A0"/>
+        <fgColor rgb="00C0392B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D35400"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C0392B"/>
       </patternFill>
     </fill>
     <fill>
@@ -88,6 +83,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00CB4335"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAD7A0"/>
       </patternFill>
     </fill>
     <fill>
@@ -103,11 +103,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00B9772B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0095A5A6"/>
       </patternFill>
     </fill>
     <fill>
@@ -142,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -190,9 +185,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -560,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -647,17 +639,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>COURT-N-1</t>
+          <t>FIELD-NE</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>北侧篮球场群</t>
+          <t>东北田径场</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>室外球场</t>
+          <t>室外运动场</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -666,28 +658,28 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>118.05</v>
+        <v>112.35</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>7.73</v>
+        <v>25.23</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>16.46</v>
+        <v>29.12</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>9.51</v>
+        <v>26.79</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>ellipse</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>田径场北侧室外篮球场（多片）。</t>
+          <t>标准足球场+环形跑道+看台，位于校园东北角。</t>
         </is>
       </c>
     </row>
@@ -699,17 +691,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>COURT-N-2</t>
+          <t>SVC-NORTH</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>北侧网球场群</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>室外球场</t>
+          <t>北区综合服务楼</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>服务配套</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -718,19 +710,19 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>118.05</v>
+        <v>50.94</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>17.24</v>
+        <v>32.79</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>16.46</v>
+        <v>18.36</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>17.72</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -739,7 +731,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>田径场北侧室外网球场（多片）。</t>
+          <t>北部中轴西侧综合服务楼（名称待核对，含停车场）。</t>
         </is>
       </c>
     </row>
@@ -751,17 +743,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FIELD-NE</t>
+          <t>SVC-N1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>东北田径场</t>
+          <t>北区服务楼A</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>室外运动场</t>
+          <t>服务配套</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -770,28 +762,28 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>112.35</v>
+        <v>7.9</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>25.23</v>
+        <v>34.95</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>29.12</v>
+        <v>19.62</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>26.79</v>
+        <v>4.32</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>ellipse</t>
+          <t>rect</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>标准足球场+环形跑道+看台，位于校园东北角。</t>
+          <t>西北侧服务/配套楼（名称待核对，邻菜鸟驿站）。</t>
         </is>
       </c>
     </row>
@@ -803,15 +795,15 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SVC-NORTH</t>
+          <t>SVC-N3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>北区综合服务楼</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
+          <t>北区服务楼C</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>服务配套</t>
         </is>
@@ -822,19 +814,19 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>50.94</v>
+        <v>28.16</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>32.79</v>
+        <v>34.95</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>18.36</v>
+        <v>15.19</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>17.72</v>
+        <v>4.32</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -843,7 +835,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>北部中轴西侧综合服务楼（名称待核对，含停车场）。</t>
+          <t>西北侧服务/配套楼（名称待核对）。</t>
         </is>
       </c>
     </row>
@@ -855,15 +847,15 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SVC-N1</t>
+          <t>SVC-N2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>北区服务楼A</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+          <t>北区服务楼B</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>服务配套</t>
         </is>
@@ -877,7 +869,7 @@
         <v>7.9</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>34.95</v>
+        <v>41.87</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>19.62</v>
@@ -895,7 +887,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>西北侧服务/配套楼（名称待核对，邻菜鸟驿站）。</t>
+          <t>西北侧服务/配套楼（名称待核对）。</t>
         </is>
       </c>
     </row>
@@ -907,15 +899,15 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SVC-N3</t>
+          <t>SVC-N4</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>北区服务楼C</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+          <t>北区服务楼D</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>服务配套</t>
         </is>
@@ -929,10 +921,10 @@
         <v>28.16</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>34.95</v>
+        <v>41.87</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>15.19</v>
+        <v>17.09</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>4.32</v>
@@ -959,17 +951,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SVC-N2</t>
+          <t>COURT-ENG</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>北区服务楼B</t>
+          <t>工程训练中心球场</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>服务配套</t>
+          <t>室外球场</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -978,19 +970,19 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>7.9</v>
+        <v>100.64</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>41.87</v>
+        <v>45.76</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>19.62</v>
+        <v>25.95</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4.32</v>
+        <v>11.24</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -999,7 +991,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>西北侧服务/配套楼（名称待核对）。</t>
+          <t>工程训练中心西侧篮球场/网球场（黄色块）。</t>
         </is>
       </c>
     </row>
@@ -1011,15 +1003,15 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SVC-N4</t>
+          <t>ENG-TRAIN</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>北区服务楼D</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
+          <t>工程训练中心</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>服务配套</t>
         </is>
@@ -1030,19 +1022,19 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>28.16</v>
+        <v>93.36</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>41.87</v>
+        <v>56.13</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>17.09</v>
+        <v>18.36</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4.32</v>
+        <v>12.96</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1051,7 +1043,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>西北侧服务/配套楼（名称待核对）。</t>
+          <t>东北侧工程训练中心，含工程实践教学场地与配套停车场。</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1055,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>COURT-ENG</t>
+          <t>DORM-YH2</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>工程训练中心球场</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>室外球场</t>
+          <t>樱花苑2号楼</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>学生公寓</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1082,19 +1074,19 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>100.64</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>45.76</v>
+        <v>69.53</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>25.95</v>
+        <v>14.56</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>11.24</v>
+        <v>12.96</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1103,7 +1095,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>工程训练中心西侧篮球场/网球场（黄色块）。</t>
+          <t>本科四人间，上床下桌、空调、独立卫浴；内设烛光超市。</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1107,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ENG-TRAIN</t>
+          <t>DORM-YH4</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>工程训练中心</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>服务配套</t>
+          <t>樱花苑4号楼</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>学生公寓</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1134,19 +1126,19 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>93.36</v>
+        <v>24.99</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>56.13</v>
+        <v>69.53</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>18.36</v>
+        <v>14.56</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>12.96</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1155,7 +1147,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>东北侧工程训练中心，含工程实践教学场地与配套停车场。</t>
+          <t>本科四人间，楼下设水果超市。</t>
         </is>
       </c>
     </row>
@@ -1167,38 +1159,38 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>DORM-PG</t>
+          <t>TEACH-2</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>研究生宿舍</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>在建</t>
+          <t>第二教学楼</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>教学楼</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>已建</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>61.07</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>59.59</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>30.39</v>
+        <v>24.69</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>9.94</v>
+        <v>15.56</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1207,7 +1199,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>西北侧研究生公寓（图中示为在建）。</t>
+          <t>柳湖东北侧大型教学楼，承担本科课堂教学。</t>
         </is>
       </c>
     </row>
@@ -1219,17 +1211,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>COURT-MID</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>中部篮球场</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>室外球场</t>
+          <t>大学生活动中心</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>活动/报告厅</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1238,19 +1230,19 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45.25</v>
+        <v>38.28</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>60.88</v>
+        <v>82.92</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>25.95</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>12.96</v>
+        <v>11.24</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1259,7 +1251,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>研究生宿舍东侧、音乐厅北侧篮球场（黄色块）。</t>
+          <t>柳湖西北异形建筑，学生社团与活动场所。</t>
         </is>
       </c>
     </row>
@@ -1271,38 +1263,38 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>HALL-MUSIC</t>
+          <t>DORM-YH1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>音乐厅</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>活动/报告厅</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>在建</t>
+          <t>樱花苑1号楼</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>学生公寓</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>已建</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45.88</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>68.23</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>18.36</v>
+        <v>14.56</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>14.69</v>
+        <v>13.83</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1311,7 +1303,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>研究生宿舍东侧（图中示为在建）。</t>
+          <t>本科四人间，设烛光超市。</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1315,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>DORM-YH2</t>
+          <t>DORM-YH3</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>樱花苑2号楼</t>
+          <t>樱花苑3号楼</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1342,16 +1334,16 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>24.99</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>69.53</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>14.56</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>12.96</v>
+        <v>13.83</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>7</v>
@@ -1363,7 +1355,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>本科四人间，上床下桌、空调、独立卫浴；内设烛光超市。</t>
+          <t>本科四人间，北侧即紫竹餐厅。</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1367,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>DORM-YH4</t>
+          <t>SVC-LOGI</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>樱花苑4号楼</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
+          <t>后勤服务楼</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>服务配套</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1394,19 +1386,19 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>24.99</v>
+        <v>9.17</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>69.53</v>
+        <v>85.09</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>14.56</v>
+        <v>20.89</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>12.96</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -1415,7 +1407,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>本科四人间，楼下设水果超市。</t>
+          <t>后勤服务、配套办公，邻地面停车场。</t>
         </is>
       </c>
     </row>
@@ -1427,17 +1419,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>TEACH-2</t>
+          <t>LIB</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>第二教学楼</t>
+          <t>图书馆</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>教学楼</t>
+          <t>图书馆</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1446,19 +1438,19 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>61.07</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>76.01000000000001</v>
+        <v>88.97</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>24.69</v>
+        <v>18.36</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>15.56</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -1467,7 +1459,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>柳湖东北侧大型教学楼，承担本科课堂教学。</t>
+          <t>约5万㎡，红色层叠盒体+玻璃幕墙，临柳湖，含自习区/研讨室/创客空间/视听室。</t>
         </is>
       </c>
     </row>
@@ -1479,17 +1471,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>GATE-E</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>大学生活动中心</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>活动/报告厅</t>
+          <t>东门</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>校门</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1498,19 +1490,19 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>38.28</v>
+        <v>140.83</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>82.92</v>
+        <v>88.97</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>25.95</v>
+        <v>3.8</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>11.24</v>
+        <v>6.48</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -1519,7 +1511,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>柳湖西北异形建筑，学生社团与活动场所。</t>
+          <t>校园东侧出入口，车辆主出入口，紧邻机动车环岛。</t>
         </is>
       </c>
     </row>
@@ -1531,17 +1523,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>DORM-YH1</t>
+          <t>CAN-ZIZHU</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>樱花苑1号楼</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
+          <t>紫竹餐厅</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>食堂</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1550,19 +1542,19 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>22.46</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>84.65000000000001</v>
+        <v>94.59</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>14.56</v>
+        <v>11.39</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>13.83</v>
+        <v>11.24</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -1571,7 +1563,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>本科四人间，设烛光超市。</t>
+          <t>樱花苑3号楼北侧，含紫竹一~四食堂及民族食堂，约3900座。</t>
         </is>
       </c>
     </row>
@@ -1583,17 +1575,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>DORM-YH3</t>
+          <t>GATE-W</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>樱花苑3号楼</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
+          <t>西门</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>校门</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1602,19 +1594,19 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>24.99</v>
+        <v>5.37</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>84.65000000000001</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>14.56</v>
+        <v>4.43</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>13.83</v>
+        <v>6.05</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -1623,7 +1615,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>本科四人间，北侧即紫竹餐厅。</t>
+          <t>校园西侧出入口，邻后勤服务楼与地面停车场，樱花苑生活片区主要人行入口。</t>
         </is>
       </c>
     </row>
@@ -1635,35 +1627,35 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SVC-LOGI</t>
+          <t>TEACH-PUB</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>后勤服务楼</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>服务配套</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
+          <t>公共教学楼（报告厅）</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>教学楼</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>在建</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>9.17</v>
+        <v>57.28</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>85.09</v>
+        <v>95.89</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>20.89</v>
+        <v>14.56</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>4</v>
@@ -1675,7 +1667,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>后勤服务、配套办公，邻地面停车场。</t>
+          <t>柳湖西岸公共教学楼，含报告厅（图中示为在建）。</t>
         </is>
       </c>
     </row>
@@ -1687,38 +1679,38 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>COL-WENLI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>图书馆</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>图书馆</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
+          <t>文理楼</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>学院楼</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>在建</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>77.84999999999999</v>
+        <v>96.52</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>88.97</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>18.36</v>
+        <v>20.26</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15.56</v>
+        <v>13.83</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -1727,7 +1719,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>约5万㎡，红色层叠盒体+玻璃幕墙，临柳湖，含自习区/研讨室/创客空间/视听室。</t>
+          <t>2023年建成，经管/数理/文法/马院教学科研楼，约2万㎡（图中示为在建）。</t>
         </is>
       </c>
     </row>
@@ -1739,17 +1731,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GATE-E</t>
+          <t>DORM-YH6</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>东门</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>校门</t>
+          <t>樱花苑6号楼</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>学生公寓</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1758,19 +1750,19 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>140.83</v>
+        <v>7.9</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>88.97</v>
+        <v>106.69</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>3.8</v>
+        <v>16.46</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6.48</v>
+        <v>12.96</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -1779,7 +1771,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>校园东侧出入口，车辆主出入口，紧邻机动车环岛。</t>
+          <t>本科四人间（编号位置以官方图为准，待核对）。</t>
         </is>
       </c>
     </row>
@@ -1791,17 +1783,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CAN-ZIZHU</t>
+          <t>DORM-YH5</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>紫竹餐厅</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>食堂</t>
+          <t>樱花苑5号楼</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>学生公寓</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1810,19 +1802,19 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>22.46</v>
+        <v>24.36</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>94.59</v>
+        <v>106.69</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>11.39</v>
+        <v>15.83</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>11.24</v>
+        <v>12.96</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -1831,7 +1823,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>樱花苑3号楼北侧，含紫竹一~四食堂及民族食堂，约3900座。</t>
+          <t>本科四人间，内设1958咖啡厅。</t>
         </is>
       </c>
     </row>
@@ -1843,38 +1835,38 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TEACH-PUB</t>
+          <t>PLAZA-HONGDE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>公共教学楼（报告厅）</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>教学楼</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>在建</t>
+          <t>宏德广场</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>广场</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>已建</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>57.28</v>
+        <v>66.77</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>95.89</v>
+        <v>106.69</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>14.56</v>
+        <v>15.83</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>12.1</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1875,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>柳湖西岸公共教学楼，含报告厅（图中示为在建）。</t>
+          <t>图书馆西南、柳湖东侧礼仪广场。</t>
         </is>
       </c>
     </row>
@@ -1895,38 +1887,38 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>COL-WENLI</t>
+          <t>LIUHU-SHUYUAN</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>文理楼</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>学院楼</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>在建</t>
+          <t>柳湖书院</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>活动/报告厅</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>已建</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>96.52</v>
+        <v>47.78</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>96.31999999999999</v>
+        <v>107.99</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>20.26</v>
+        <v>16.46</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>13.83</v>
+        <v>7.35</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -1935,7 +1927,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2023年建成，经管/数理/文法/马院教学科研楼，约2万㎡（图中示为在建）。</t>
+          <t>柳湖西南侧小型书院/文化空间。</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1939,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>DORM-YH6</t>
+          <t>DORM-YL</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>樱花苑6号楼</t>
+          <t>玉兰苑1-2号楼</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -1966,19 +1958,19 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>7.9</v>
+        <v>45.25</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>106.69</v>
+        <v>111.02</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>16.46</v>
+        <v>20.26</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>12.96</v>
+        <v>20.74</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -1987,7 +1979,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>本科四人间（编号位置以官方图为准，待核对）。</t>
+          <t>学生公寓（1/2号楼），含超市配套。</t>
         </is>
       </c>
     </row>
@@ -1999,17 +1991,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>DORM-YH5</t>
+          <t>LAB-H</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>樱花苑5号楼</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
+          <t>实验楼H</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>实验/科研楼</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2018,19 +2010,19 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>24.36</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>106.69</v>
+        <v>112.1</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>15.83</v>
+        <v>36.72</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>12.96</v>
+        <v>3.24</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -2039,7 +2031,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>本科四人间，内设1958咖啡厅。</t>
+          <t>东南科研实验群北排（编号按2021官方图，待与现状核对）。</t>
         </is>
       </c>
     </row>
@@ -2051,17 +2043,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>PLAZA-HONGDE</t>
+          <t>LAB-G</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>宏德广场</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>广场</t>
+          <t>实验楼G</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>实验/科研楼</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2070,19 +2062,19 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>66.77</v>
+        <v>110.45</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>106.69</v>
+        <v>115.34</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>15.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -2091,7 +2083,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>图书馆西南、柳湖东侧礼仪广场。</t>
+          <t>东南科研实验群东翼（编号待核对）。</t>
         </is>
       </c>
     </row>
@@ -2103,17 +2095,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>LIUHU-SHUYUAN</t>
+          <t>LAB-TECH</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>柳湖书院</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>活动/报告厅</t>
+          <t>科技创新楼</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>实验/科研楼</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2122,19 +2114,19 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>47.78</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>107.99</v>
+        <v>116.42</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>16.46</v>
+        <v>6.33</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7.35</v>
+        <v>18.58</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -2143,7 +2135,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>柳湖西南侧小型书院/文化空间。</t>
+          <t>实验群西翼竖楼（名称待核对，或为科技创新研究院）。</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2147,17 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>DORM-YL</t>
+          <t>LAB-F</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>玉兰苑1-2号楼</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
+          <t>实验楼F</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>实验/科研楼</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2174,19 +2166,19 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45.25</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>111.02</v>
+        <v>117.5</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>20.26</v>
+        <v>21.52</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.74</v>
+        <v>3.24</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -2195,7 +2187,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>学生公寓（1/2号楼），含超市配套。</t>
+          <t>东南科研实验群。</t>
         </is>
       </c>
     </row>
@@ -2207,17 +2199,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>LAB-H</t>
+          <t>DORM-YH7</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>实验楼H</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>实验/科研楼</t>
+          <t>樱花苑7号楼</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>学生公寓</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2226,19 +2218,19 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>112.1</v>
+        <v>120.95</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>36.72</v>
+        <v>31.65</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3.24</v>
+        <v>11.24</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -2247,7 +2239,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>东南科研实验群北排（编号按2021官方图，待与现状核对）。</t>
+          <t>本科四人间，设烛光超市。</t>
         </is>
       </c>
     </row>
@@ -2259,12 +2251,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>LAB-G</t>
+          <t>LAB-E</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>实验楼G</t>
+          <t>实验楼E</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
@@ -2278,16 +2270,16 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>110.45</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>115.34</v>
+        <v>124.63</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>8.859999999999999</v>
+        <v>21.52</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>12.1</v>
+        <v>3.24</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>5</v>
@@ -2299,7 +2291,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>东南科研实验群东翼（编号待核对）。</t>
+          <t>东南科研实验群。</t>
         </is>
       </c>
     </row>
@@ -2311,12 +2303,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>LAB-TECH</t>
+          <t>LAB-D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>科技创新楼</t>
+          <t>实验楼D</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
@@ -2330,16 +2322,16 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>108.55</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>116.42</v>
+        <v>127.22</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>6.33</v>
+        <v>10.13</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>18.58</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>5</v>
@@ -2351,7 +2343,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>实验群西翼竖楼（名称待核对，或为科技创新研究院）。</t>
+          <t>科研实验群东南翼（编号待核对）。</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2355,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>LAB-F</t>
+          <t>LAB-C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>实验楼F</t>
+          <t>实验楼C</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -2385,10 +2377,10 @@
         <v>88.93000000000001</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>117.5</v>
+        <v>131.76</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>21.52</v>
+        <v>19.62</v>
       </c>
       <c r="I35" s="2" t="n">
         <v>3.24</v>
@@ -2415,17 +2407,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>DORM-YH7</t>
+          <t>GYM-BASKET</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>樱花苑7号楼</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
+          <t>篮球馆</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>体育馆</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2434,19 +2426,19 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>7.9</v>
+        <v>39.55</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>120.95</v>
+        <v>133.49</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>31.65</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11.24</v>
+        <v>9.51</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -2455,7 +2447,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>本科四人间，设烛光超市。</t>
+          <t>西南田径场东侧室内球类馆。</t>
         </is>
       </c>
     </row>
@@ -2467,17 +2459,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>LAB-E</t>
+          <t>GYM-TENNIS</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>实验楼E</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>实验/科研楼</t>
+          <t>网球馆</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>体育馆</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2486,19 +2478,19 @@
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>88.93000000000001</v>
+        <v>49.05</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>124.63</v>
+        <v>133.49</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>21.52</v>
+        <v>9.5</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3.24</v>
+        <v>9.51</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -2507,7 +2499,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>东南科研实验群。</t>
+          <t>西南田径场东侧室内网球馆（名称待核对）。</t>
         </is>
       </c>
     </row>
@@ -2519,17 +2511,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>LAB-D</t>
+          <t>TEACH-1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>实验楼D</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>实验/科研楼</t>
+          <t>第一教学楼</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>教学楼</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2538,28 +2530,28 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>108.55</v>
+        <v>61.07</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>127.22</v>
+        <v>138.03</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10.13</v>
+        <v>38.61</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>5</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>arc</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>科研实验群东南翼（编号待核对）。</t>
+          <t>弧形围合主教学楼，130间智慧教室，中央架空门廊；分A座(东)、B座(西)。</t>
         </is>
       </c>
     </row>
@@ -2571,17 +2563,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PARK-E</t>
+          <t>FIELD-SW</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>东侧停车场</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>停车场</t>
+          <t>西南田径场（风雨操场）</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>室外运动场</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2590,28 +2582,28 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>124.38</v>
+        <v>7.27</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>128.3</v>
+        <v>138.24</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>17.72</v>
+        <v>36.72</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>19.88</v>
+        <v>31.12</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>ellipse</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>东南大型地面停车场。</t>
+          <t>樱花苑南侧，标准足球场+环形跑道。</t>
         </is>
       </c>
     </row>
@@ -2623,17 +2615,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>LAB-C</t>
+          <t>GYM-SWIM</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>实验楼C</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>实验/科研楼</t>
+          <t>游泳馆</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>体育馆</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2642,19 +2634,19 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>88.93000000000001</v>
+        <v>39.55</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>131.76</v>
+        <v>142.99</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>19.62</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>3.24</v>
+        <v>9.51</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -2663,7 +2655,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>东南科研实验群。</t>
+          <t>西南田径场东侧室内游泳馆（名称待核对）。</t>
         </is>
       </c>
     </row>
@@ -2675,15 +2667,15 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>GYM-BASKET</t>
+          <t>GYM-EXTRA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>篮球馆</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
+          <t>球类训练馆</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>体育馆</t>
         </is>
@@ -2694,16 +2686,16 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>39.55</v>
+        <v>49.05</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>133.49</v>
+        <v>142.99</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>8.859999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>9.51</v>
+        <v>11.24</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>2</v>
@@ -2715,7 +2707,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>西南田径场东侧室内球类馆。</t>
+          <t>西南田径场东侧排球/训练馆（名称待核对）。</t>
         </is>
       </c>
     </row>
@@ -2727,17 +2719,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>GYM-TENNIS</t>
+          <t>SVC-SW</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>网球馆</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>体育馆</t>
+          <t>西南附属用房</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>服务配套</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2746,16 +2738,16 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>49.05</v>
+        <v>43.35</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>133.49</v>
+        <v>147.32</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>9.5</v>
+        <v>14.56</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>9.51</v>
+        <v>6.48</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>2</v>
@@ -2767,7 +2759,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>西南田径场东侧室内网球馆（名称待核对）。</t>
+          <t>田径场东南、南湖西侧附属设备用房（名称待核对）。</t>
         </is>
       </c>
     </row>
@@ -2779,17 +2771,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>TEACH-1</t>
+          <t>GYM</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>第一教学楼</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>教学楼</t>
+          <t>体育馆</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>体育馆</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2798,28 +2790,28 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>61.07</v>
+        <v>45.88</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>138.03</v>
+        <v>152.5</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>38.61</v>
+        <v>29.12</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>10.8</v>
+        <v>17.29</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>arc</t>
+          <t>ellipse</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>弧形围合主教学楼，130间智慧教室，中央架空门廊；分A座(东)、B座(西)。</t>
+          <t>椭圆船形综合体育馆，含篮球/羽毛球/网球/乒乓球等14个训练馆。</t>
         </is>
       </c>
     </row>
@@ -2831,17 +2823,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>FIELD-SW</t>
+          <t>GATE-S</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>西南田径场（风雨操场）</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>室外运动场</t>
+          <t>主校门（南门）</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>校门</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2850,286 +2842,26 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>7.27</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>138.24</v>
+        <v>174.11</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>36.72</v>
+        <v>14.56</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>31.12</v>
+        <v>3.46</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>ellipse</t>
+          <t>rect</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>樱花苑南侧，标准足球场+环形跑道。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>GYM-SWIM</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>游泳馆</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>体育馆</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>39.55</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>142.99</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>西南田径场东侧室内游泳馆（名称待核对）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>GYM-EXTRA</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>球类训练馆</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="inlineStr">
-        <is>
-          <t>体育馆</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>49.05</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>142.99</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>11.24</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>西南田径场东侧排球/训练馆（名称待核对）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>SVC-SW</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>西南附属用房</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>服务配套</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>43.35</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>147.32</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>田径场东南、南湖西侧附属设备用房（名称待核对）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>GYM</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>体育馆</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="inlineStr">
-        <is>
-          <t>体育馆</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>45.88</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>29.12</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>17.29</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>ellipse</t>
-        </is>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>椭圆船形综合体育馆，含篮球/羽毛球/网球/乒乓球等14个训练馆。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>GATE-S</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>主校门（南门）</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>校门</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>70.56999999999999</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>174.11</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
         <is>
           <t>学校正门、行人主出入口，校名石与『南涧路29号』标识，中轴礼仪序列起点。</t>
         </is>
@@ -3539,7 +3271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3571,9 +3303,9 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>#C0392B</t>
         </is>
@@ -3588,7 +3320,7 @@
       <c r="B3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>#C0392B</t>
         </is>
@@ -3603,7 +3335,7 @@
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>#A93226</t>
         </is>
@@ -3646,7 +3378,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
@@ -3661,7 +3393,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -3678,7 +3410,7 @@
       <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>#CB4335</t>
         </is>
@@ -3693,7 +3425,7 @@
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>#5D6D7E</t>
         </is>
@@ -3708,7 +3440,7 @@
       <c r="B11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>#922B21</t>
         </is>
@@ -3723,7 +3455,7 @@
       <c r="B12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>#2E86C1</t>
         </is>
@@ -3736,9 +3468,9 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>#5DADE2</t>
         </is>
@@ -3756,21 +3488,6 @@
       <c r="C14" s="14" t="inlineStr">
         <is>
           <t>#C9C2B2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>停车场</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>#95A5A6</t>
         </is>
       </c>
     </row>

--- a/02_地图工程/建筑点位台账.xlsx
+++ b/02_地图工程/建筑点位台账.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -47,22 +47,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E86C1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="005D6D7E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005DADE2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007D6B91"/>
       </patternFill>
     </fill>
     <fill>
@@ -82,27 +67,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="009E4A30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00CB4335"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAD7A0"/>
+        <fgColor rgb="00B9772B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B35035"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C9C2B2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B9772B"/>
+        <fgColor rgb="002E86C1"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -173,18 +153,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -552,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -639,17 +607,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FIELD-NE</t>
+          <t>ENG-TRAIN</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>东北田径场</t>
+          <t>泰瑞楼（工程训练中心）</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>室外运动场</t>
+          <t>服务配套</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -658,28 +626,28 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>112.35</v>
+        <v>93.36</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>25.23</v>
+        <v>56.13</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>29.12</v>
+        <v>18.36</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26.79</v>
+        <v>12.96</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>ellipse</t>
+          <t>rect</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>标准足球场+环形跑道+看台，位于校园东北角。</t>
+          <t>东北侧工程训练中心『泰瑞楼』（泰瑞机器冠名捐赠），工程实践教学场地。</t>
         </is>
       </c>
     </row>
@@ -691,17 +659,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SVC-NORTH</t>
+          <t>TEACH-2</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>北区综合服务楼</t>
+          <t>第二教学楼</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>服务配套</t>
+          <t>教学楼</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -710,16 +678,16 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>50.94</v>
+        <v>61.07</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>32.79</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>18.36</v>
+        <v>24.69</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>17.72</v>
+        <v>15.56</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>5</v>
@@ -731,7 +699,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>北部中轴西侧综合服务楼（名称待核对，含停车场）。</t>
+          <t>柳湖东北侧大型教学楼，承担本科课堂教学。</t>
         </is>
       </c>
     </row>
@@ -743,17 +711,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SVC-N1</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>北区服务楼A</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>服务配套</t>
+          <t>大学生活动中心</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>活动/报告厅</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -762,16 +730,16 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>7.9</v>
+        <v>38.28</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>34.95</v>
+        <v>82.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>19.62</v>
+        <v>25.95</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4.32</v>
+        <v>11.24</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>3</v>
@@ -783,7 +751,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>西北侧服务/配套楼（名称待核对，邻菜鸟驿站）。</t>
+          <t>柳湖西北异形建筑，学生社团与活动场所，与校史馆相邻。</t>
         </is>
       </c>
     </row>
@@ -795,15 +763,15 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SVC-N3</t>
+          <t>SVC-LOGI</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>北区服务楼C</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+          <t>后勤服务楼</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>服务配套</t>
         </is>
@@ -814,19 +782,19 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>28.16</v>
+        <v>9.17</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>34.95</v>
+        <v>85.09</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>15.19</v>
+        <v>20.89</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4.32</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -835,7 +803,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>西北侧服务/配套楼（名称待核对）。</t>
+          <t>后勤服务、配套办公，邻地面停车场。</t>
         </is>
       </c>
     </row>
@@ -847,17 +815,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SVC-N2</t>
+          <t>LIB</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>北区服务楼B</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>服务配套</t>
+          <t>图书馆</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>图书馆</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -866,19 +834,19 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>7.9</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>41.87</v>
+        <v>88.97</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>19.62</v>
+        <v>18.36</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4.32</v>
+        <v>15.56</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -887,7 +855,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>西北侧服务/配套楼（名称待核对）。</t>
+          <t>约5万㎡，红色层叠盒体+玻璃幕墙，临柳湖，含自习区/研讨室/创客空间/视听室。</t>
         </is>
       </c>
     </row>
@@ -899,17 +867,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SVC-N4</t>
+          <t>GATE-E</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>北区服务楼D</t>
+          <t>东门</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>服务配套</t>
+          <t>校门</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -918,19 +886,19 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>28.16</v>
+        <v>140.83</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>41.87</v>
+        <v>88.97</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>17.09</v>
+        <v>3.8</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4.32</v>
+        <v>6.48</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -939,7 +907,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>西北侧服务/配套楼（名称待核对）。</t>
+          <t>校园东侧出入口，车辆主出入口，紧邻机动车环岛。</t>
         </is>
       </c>
     </row>
@@ -951,17 +919,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COURT-ENG</t>
+          <t>MUSEUM-HISTORY</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>工程训练中心球场</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>室外球场</t>
+          <t>校史馆</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>校史馆/展馆</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -970,28 +938,28 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>100.64</v>
+        <v>39.87</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>45.76</v>
+        <v>94.38</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>25.95</v>
+        <v>14.56</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11.24</v>
+        <v>9.51</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>ellipse</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>工程训练中心西侧篮球场/网球场（黄色块）。</t>
+          <t>柳湖沿畔圆形红棕展馆（2025年11月竣工，约2700㎡），与大学生活动中心相邻、临柳湖；校史陈列、研究与展览的校园文化空间。</t>
         </is>
       </c>
     </row>
@@ -1003,17 +971,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ENG-TRAIN</t>
+          <t>CAN-ZIZHU</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>工程训练中心</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>服务配套</t>
+          <t>紫竹餐厅（食堂）</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>食堂</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1022,19 +990,19 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>93.36</v>
+        <v>22.46</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>56.13</v>
+        <v>94.59</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>18.36</v>
+        <v>11.39</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>12.96</v>
+        <v>11.24</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1043,7 +1011,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>东北侧工程训练中心，含工程实践教学场地与配套停车场。</t>
+          <t>樱花苑3号楼北侧，含紫竹一~四食堂及民族食堂，约3900座。</t>
         </is>
       </c>
     </row>
@@ -1055,17 +1023,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>DORM-YH2</t>
+          <t>GATE-W</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>樱花苑2号楼</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
+          <t>西门</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>校门</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1074,19 +1042,19 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>5.37</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>69.53</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>14.56</v>
+        <v>4.43</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>12.96</v>
+        <v>6.05</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1095,7 +1063,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>本科四人间，上床下桌、空调、独立卫浴；内设烛光超市。</t>
+          <t>校园西侧出入口，邻后勤服务楼与地面停车场，樱花苑生活片区主要人行入口。</t>
         </is>
       </c>
     </row>
@@ -1107,17 +1075,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DORM-YH4</t>
+          <t>LAB-H</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>樱花苑4号楼</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
+          <t>实验楼H</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>实验/科研楼</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1126,19 +1094,19 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>24.99</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>69.53</v>
+        <v>112.1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>14.56</v>
+        <v>36.72</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>12.96</v>
+        <v>3.24</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1147,7 +1115,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>本科四人间，楼下设水果超市。</t>
+          <t>东南科研实验群北排（编号按2021官方图，待与现状核对）。</t>
         </is>
       </c>
     </row>
@@ -1159,17 +1127,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>TEACH-2</t>
+          <t>LAB-G</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>第二教学楼</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>教学楼</t>
+          <t>实验楼G</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>实验/科研楼</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1178,16 +1146,16 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>61.07</v>
+        <v>110.45</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>76.01000000000001</v>
+        <v>115.34</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>24.69</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15.56</v>
+        <v>12.1</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>5</v>
@@ -1199,7 +1167,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>柳湖东北侧大型教学楼，承担本科课堂教学。</t>
+          <t>东南科研实验群东翼（编号待核对）。</t>
         </is>
       </c>
     </row>
@@ -1211,17 +1179,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>LAB-TECH</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>大学生活动中心</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>活动/报告厅</t>
+          <t>科技创新楼</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>实验/科研楼</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1230,19 +1198,19 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>38.28</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>82.92</v>
+        <v>116.42</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>25.95</v>
+        <v>6.33</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>11.24</v>
+        <v>18.58</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1251,7 +1219,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>柳湖西北异形建筑，学生社团与活动场所。</t>
+          <t>实验群西翼竖楼（名称待核对，或为科技创新研究院）。</t>
         </is>
       </c>
     </row>
@@ -1263,17 +1231,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>DORM-YH1</t>
+          <t>LAB-F</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>樱花苑1号楼</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
+          <t>实验楼F</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>实验/科研楼</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1282,19 +1250,19 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>84.65000000000001</v>
+        <v>117.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>14.56</v>
+        <v>21.52</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13.83</v>
+        <v>3.24</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1303,7 +1271,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>本科四人间，设烛光超市。</t>
+          <t>东南科研实验群。</t>
         </is>
       </c>
     </row>
@@ -1315,17 +1283,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>DORM-YH3</t>
+          <t>LAB-E</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>樱花苑3号楼</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
+          <t>实验楼E</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>实验/科研楼</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1334,19 +1302,19 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>24.99</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>84.65000000000001</v>
+        <v>124.63</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>14.56</v>
+        <v>21.52</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>13.83</v>
+        <v>3.24</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1355,7 +1323,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>本科四人间，北侧即紫竹餐厅。</t>
+          <t>东南科研实验群。</t>
         </is>
       </c>
     </row>
@@ -1367,17 +1335,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SVC-LOGI</t>
+          <t>LAB-D</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>后勤服务楼</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>服务配套</t>
+          <t>实验楼D</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>实验/科研楼</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1386,19 +1354,19 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>9.17</v>
+        <v>108.55</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>85.09</v>
+        <v>127.22</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>20.89</v>
+        <v>10.13</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -1407,7 +1375,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>后勤服务、配套办公，邻地面停车场。</t>
+          <t>科研实验群东南翼（编号待核对）。</t>
         </is>
       </c>
     </row>
@@ -1419,17 +1387,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>LAB-C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>图书馆</t>
+          <t>实验楼C</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>图书馆</t>
+          <t>实验/科研楼</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1438,19 +1406,19 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>77.84999999999999</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>88.97</v>
+        <v>131.76</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>18.36</v>
+        <v>19.62</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15.56</v>
+        <v>3.24</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -1459,7 +1427,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>约5万㎡，红色层叠盒体+玻璃幕墙，临柳湖，含自习区/研讨室/创客空间/视听室。</t>
+          <t>东南科研实验群。</t>
         </is>
       </c>
     </row>
@@ -1471,17 +1439,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>GATE-E</t>
+          <t>TEACH-1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>东门</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>校门</t>
+          <t>第一教学楼</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>教学楼</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1490,28 +1458,28 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>140.83</v>
+        <v>61.07</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>88.97</v>
+        <v>138.03</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3.8</v>
+        <v>38.61</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6.48</v>
+        <v>10.8</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>arc</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>校园东侧出入口，车辆主出入口，紧邻机动车环岛。</t>
+          <t>弧形围合主教学楼，130间智慧教室，中央架空门廊；分A座(东)、B座(西)。</t>
         </is>
       </c>
     </row>
@@ -1523,17 +1491,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CAN-ZIZHU</t>
+          <t>FIELD-SW</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>紫竹餐厅</t>
+          <t>操场（西南田径场）</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>食堂</t>
+          <t>室外运动场</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1542,28 +1510,28 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>22.46</v>
+        <v>7.27</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>94.59</v>
+        <v>138.24</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>11.39</v>
+        <v>36.72</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>11.24</v>
+        <v>31.12</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>ellipse</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>樱花苑3号楼北侧，含紫竹一~四食堂及民族食堂，约3900座。</t>
+          <t>樱花苑南侧、体育馆西侧，标准足球场+环形跑道（风雨操场）。</t>
         </is>
       </c>
     </row>
@@ -1575,17 +1543,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>GATE-W</t>
+          <t>GYM</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>西门</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>校门</t>
+          <t>体育馆</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>体育馆</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1594,28 +1562,28 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5.37</v>
+        <v>45.88</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>95.45999999999999</v>
+        <v>152.5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>4.43</v>
+        <v>29.12</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>6.05</v>
+        <v>17.29</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>ellipse</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>校园西侧出入口，邻后勤服务楼与地面停车场，樱花苑生活片区主要人行入口。</t>
+          <t>椭圆船形综合体育馆，含篮球/羽毛球/网球/乒乓球等14个训练馆。</t>
         </is>
       </c>
     </row>
@@ -1627,38 +1595,38 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>TEACH-PUB</t>
+          <t>GATE-S</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>公共教学楼（报告厅）</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>教学楼</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>在建</t>
+          <t>主校门（南门）</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>校门</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>已建</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>57.28</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>95.89</v>
+        <v>174.11</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>14.56</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>12.1</v>
+        <v>3.46</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -1666,1202 +1634,6 @@
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>柳湖西岸公共教学楼，含报告厅（图中示为在建）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>COL-WENLI</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>文理楼</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>学院楼</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>在建</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>96.52</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>96.31999999999999</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>13.83</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>2023年建成，经管/数理/文法/马院教学科研楼，约2万㎡（图中示为在建）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>DORM-YH6</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>樱花苑6号楼</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>106.69</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>16.46</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>本科四人间（编号位置以官方图为准，待核对）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>DORM-YH5</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>樱花苑5号楼</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>24.36</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>106.69</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>本科四人间，内设1958咖啡厅。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>PLAZA-HONGDE</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>宏德广场</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>广场</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>66.77</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>106.69</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>图书馆西南、柳湖东侧礼仪广场。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>LIUHU-SHUYUAN</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>柳湖书院</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>活动/报告厅</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>47.78</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>107.99</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>16.46</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>柳湖西南侧小型书院/文化空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>DORM-YL</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>玉兰苑1-2号楼</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>45.25</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>111.02</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>20.74</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>学生公寓（1/2号楼），含超市配套。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>LAB-H</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>实验楼H</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>实验/科研楼</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>112.1</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>36.72</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>东南科研实验群北排（编号按2021官方图，待与现状核对）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>LAB-G</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>实验楼G</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>实验/科研楼</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>110.45</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>115.34</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>东南科研实验群东翼（编号待核对）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>LAB-TECH</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>科技创新楼</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>实验/科研楼</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>116.42</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>18.58</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>实验群西翼竖楼（名称待核对，或为科技创新研究院）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>LAB-F</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>实验楼F</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>实验/科研楼</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>88.93000000000001</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>117.5</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>21.52</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>东南科研实验群。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>DORM-YH7</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>樱花苑7号楼</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>学生公寓</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>120.95</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>11.24</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>本科四人间，设烛光超市。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>LAB-E</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>实验楼E</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>实验/科研楼</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>88.93000000000001</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>124.63</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>21.52</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>东南科研实验群。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>LAB-D</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>实验楼D</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>实验/科研楼</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>108.55</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>127.22</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>科研实验群东南翼（编号待核对）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>LAB-C</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>实验楼C</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>实验/科研楼</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>88.93000000000001</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>131.76</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>19.62</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>东南科研实验群。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>GYM-BASKET</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>篮球馆</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>体育馆</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>39.55</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>133.49</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>西南田径场东侧室内球类馆。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>GYM-TENNIS</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>网球馆</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>体育馆</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>49.05</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>133.49</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>西南田径场东侧室内网球馆（名称待核对）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>TEACH-1</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>第一教学楼</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>教学楼</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>61.07</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>138.03</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>38.61</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>arc</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>弧形围合主教学楼，130间智慧教室，中央架空门廊；分A座(东)、B座(西)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>FIELD-SW</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>西南田径场（风雨操场）</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>室外运动场</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>138.24</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>36.72</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>31.12</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>ellipse</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>樱花苑南侧，标准足球场+环形跑道。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>GYM-SWIM</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>游泳馆</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>体育馆</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>39.55</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>142.99</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>西南田径场东侧室内游泳馆（名称待核对）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>GYM-EXTRA</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>球类训练馆</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <t>体育馆</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>49.05</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>142.99</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>11.24</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>西南田径场东侧排球/训练馆（名称待核对）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>SVC-SW</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>西南附属用房</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>服务配套</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>43.35</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>147.32</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>田径场东南、南湖西侧附属设备用房（名称待核对）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>GYM</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>体育馆</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>体育馆</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>45.88</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>29.12</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>17.29</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>ellipse</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>椭圆船形综合体育馆，含篮球/羽毛球/网球/乒乓球等14个训练馆。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>GATE-S</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>主校门（南门）</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>校门</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>70.56999999999999</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>174.11</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
         <is>
           <t>学校正门、行人主出入口，校名石与『南涧路29号』标识，中轴礼仪序列起点。</t>
         </is>
@@ -2878,7 +1650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3084,19 +1856,19 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>菜鸟驿站</t>
+          <t>ATM</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>express</t>
+          <t>atm</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10.43</v>
+        <v>91.14</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>37.55</v>
+        <v>103.45</v>
       </c>
     </row>
     <row r="10">
@@ -3107,19 +1879,19 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>烛光超市</t>
+          <t>班车站点</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>market</t>
+          <t>bus</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>29.42</v>
+        <v>80.06</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>107.77</v>
+        <v>52.67</v>
       </c>
     </row>
     <row r="11">
@@ -3130,19 +1902,19 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1958咖啡厅</t>
+          <t>湖心亭</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>coffee</t>
+          <t>sight</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>31</v>
+        <v>80.06</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>115.34</v>
+        <v>106.69</v>
       </c>
     </row>
     <row r="12">
@@ -3153,19 +1925,19 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ATM</t>
+          <t>燕贺亭</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>atm</t>
+          <t>sight</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>91.14</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>103.45</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="13">
@@ -3176,87 +1948,18 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>班车站点</t>
+          <t>国旗广场</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>bus</t>
+          <t>sight</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>80.06</v>
+        <v>78.8</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>52.67</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>兴趣点</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>湖心亭</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>sight</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>80.06</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>106.69</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>兴趣点</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>燕贺亭</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>sight</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>88.93000000000001</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>12.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>兴趣点</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>国旗广场</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>sight</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="E16" s="2" t="n">
         <v>119.66</v>
       </c>
     </row>
@@ -3271,7 +1974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3305,7 +2008,7 @@
       <c r="B2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>#C0392B</t>
         </is>
@@ -3318,9 +2021,9 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>#C0392B</t>
         </is>
@@ -3335,7 +2038,7 @@
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>#A93226</t>
         </is>
@@ -3350,7 +2053,7 @@
       <c r="B5" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>#B9772B</t>
         </is>
@@ -3359,15 +2062,15 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>学院楼</t>
+          <t>校史馆/展馆</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>#B35035</t>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>#9E4A30</t>
         </is>
       </c>
     </row>
@@ -3378,9 +2081,9 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>#D35400</t>
         </is>
@@ -3389,105 +2092,60 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>学生公寓</t>
+          <t>食堂</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>#7D6B91</t>
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>#CB4335</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>食堂</t>
+          <t>服务配套</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>#CB4335</t>
+        <v>2</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>#5D6D7E</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>服务配套</t>
+          <t>体育馆</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>#5D6D7E</t>
+        <v>1</v>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>#922B21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>体育馆</t>
+          <t>室外运动场</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>#922B21</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>室外运动场</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>#2E86C1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>室外球场</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>#5DADE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>广场</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>#C9C2B2</t>
         </is>
       </c>
     </row>

--- a/02_地图工程/建筑点位台账.xlsx
+++ b/02_地图工程/建筑点位台账.xlsx
@@ -629,13 +629,13 @@
         <v>93.36</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>56.13</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>18.36</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>12.96</v>
+        <v>18.99</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>4</v>
@@ -681,13 +681,13 @@
         <v>61.07</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>76.01000000000001</v>
+        <v>108.55</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>24.69</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15.56</v>
+        <v>22.79</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>5</v>
@@ -733,13 +733,13 @@
         <v>38.28</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>82.92</v>
+        <v>118.68</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>25.95</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>11.24</v>
+        <v>16.46</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>3</v>
@@ -785,13 +785,13 @@
         <v>9.17</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>85.09</v>
+        <v>121.84</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>20.89</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>12.03</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>4</v>
@@ -837,13 +837,13 @@
         <v>77.84999999999999</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>88.97</v>
+        <v>127.54</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>18.36</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15.56</v>
+        <v>22.79</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>6</v>
@@ -889,13 +889,13 @@
         <v>140.83</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>88.97</v>
+        <v>127.54</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>3.8</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6.48</v>
+        <v>9.5</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1</v>
@@ -941,13 +941,13 @@
         <v>39.87</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>94.38</v>
+        <v>135.45</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>14.56</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>9.51</v>
+        <v>13.93</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>3</v>
@@ -993,13 +993,13 @@
         <v>22.46</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>94.59</v>
+        <v>135.77</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>11.39</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11.24</v>
+        <v>16.46</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>3</v>
@@ -1045,13 +1045,13 @@
         <v>5.37</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>95.45999999999999</v>
+        <v>137.04</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>4.43</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6.05</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1</v>
@@ -1097,13 +1097,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>112.1</v>
+        <v>161.41</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>36.72</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3.24</v>
+        <v>4.75</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>5</v>
@@ -1149,13 +1149,13 @@
         <v>110.45</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>115.34</v>
+        <v>166.16</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>8.859999999999999</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>12.1</v>
+        <v>17.72</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>5</v>
@@ -1201,13 +1201,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>116.42</v>
+        <v>167.74</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>6.33</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>18.58</v>
+        <v>27.22</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>5</v>
@@ -1253,13 +1253,13 @@
         <v>88.93000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>117.5</v>
+        <v>169.32</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>21.52</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3.24</v>
+        <v>4.75</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>5</v>
@@ -1305,13 +1305,13 @@
         <v>88.93000000000001</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>124.63</v>
+        <v>179.77</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>21.52</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3.24</v>
+        <v>4.75</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>5</v>
@@ -1357,13 +1357,13 @@
         <v>108.55</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>127.22</v>
+        <v>183.56</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>10.13</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>12.66</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>5</v>
@@ -1409,13 +1409,13 @@
         <v>88.93000000000001</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>131.76</v>
+        <v>190.21</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>19.62</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3.24</v>
+        <v>4.75</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>5</v>
@@ -1461,13 +1461,13 @@
         <v>61.07</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>138.03</v>
+        <v>199.39</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>38.61</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>10.8</v>
+        <v>15.83</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>5</v>
@@ -1513,13 +1513,13 @@
         <v>7.27</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>138.24</v>
+        <v>199.71</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>36.72</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>31.12</v>
+        <v>45.58</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0</v>
@@ -1565,13 +1565,13 @@
         <v>45.88</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>152.5</v>
+        <v>220.6</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>29.12</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>17.29</v>
+        <v>25.32</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>3</v>
@@ -1617,13 +1617,13 @@
         <v>70.56999999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>174.11</v>
+        <v>252.25</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>14.56</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>3.46</v>
+        <v>5.06</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>1</v>
@@ -1707,7 +1707,7 @@
         <v>46.83</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="3">
@@ -1730,7 +1730,7 @@
         <v>7.27</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8.380000000000001</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="4">
@@ -1753,7 +1753,7 @@
         <v>7.9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>24.58</v>
+        <v>33.22</v>
       </c>
     </row>
     <row r="5">
@@ -1776,7 +1776,7 @@
         <v>58.86</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>94.81</v>
+        <v>136.09</v>
       </c>
     </row>
     <row r="6">
@@ -1799,7 +1799,7 @@
         <v>52.53</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>133.7</v>
+        <v>193.06</v>
       </c>
     </row>
     <row r="7">
@@ -1822,7 +1822,7 @@
         <v>64.87</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>104.96</v>
+        <v>150.96</v>
       </c>
     </row>
     <row r="8">
@@ -1845,7 +1845,7 @@
         <v>39.55</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>106.69</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="9">
@@ -1868,7 +1868,7 @@
         <v>91.14</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>103.45</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="10">
@@ -1891,7 +1891,7 @@
         <v>80.06</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>52.67</v>
+        <v>74.37</v>
       </c>
     </row>
     <row r="11">
@@ -1914,7 +1914,7 @@
         <v>80.06</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>106.69</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="12">
@@ -1937,7 +1937,7 @@
         <v>88.93000000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12.05</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="13">
@@ -1960,7 +1960,7 @@
         <v>78.8</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>119.66</v>
+        <v>172.49</v>
       </c>
     </row>
   </sheetData>

--- a/02_地图工程/建筑点位台账.xlsx
+++ b/02_地图工程/建筑点位台账.xlsx
@@ -47,6 +47,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="002E86C1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="005D6D7E"/>
       </patternFill>
     </fill>
@@ -78,11 +83,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00B9772B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E86C1"/>
       </patternFill>
     </fill>
     <fill>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -607,17 +607,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ENG-TRAIN</t>
+          <t>FIELD-N</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>泰瑞楼（工程训练中心）</t>
+          <t>北操场（东田径场）</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>服务配套</t>
+          <t>室外运动场</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -626,28 +626,28 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>93.36</v>
+        <v>83.55</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>79.43000000000001</v>
+        <v>30.69</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>18.36</v>
+        <v>23.42</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>18.99</v>
+        <v>30.39</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>ellipse</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>东北侧工程训练中心『泰瑞楼』（泰瑞机器冠名捐赠），工程实践教学场地。</t>
+          <t>校园东北侧东田径场（用户标注『北操场』），标准足球场+环形跑道，南北长轴，北邻游泳馆/篮球馆。</t>
         </is>
       </c>
     </row>
@@ -659,17 +659,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TEACH-2</t>
+          <t>ENG-TRAIN</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>第二教学楼</t>
+          <t>泰瑞楼（工程训练中心）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>教学楼</t>
+          <t>服务配套</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -678,28 +678,28 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>61.07</v>
+        <v>92.72</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>108.55</v>
+        <v>72.47</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>24.69</v>
+        <v>22.16</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>22.79</v>
+        <v>24.06</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>poly</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>柳湖东北侧大型教学楼，承担本科课堂教学。</t>
+          <t>东北侧工程训练中心『泰瑞楼』（泰瑞机器冠名捐赠），工程实践教学场地。</t>
         </is>
       </c>
     </row>
@@ -711,17 +711,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>TEACH-2</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>大学生活动中心</t>
+          <t>第二教学楼</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>活动/报告厅</t>
+          <t>教学楼</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -730,19 +730,19 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>38.28</v>
+        <v>61.07</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>118.68</v>
+        <v>108.23</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>25.95</v>
+        <v>27.22</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>16.46</v>
+        <v>23.74</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>柳湖西北异形建筑，学生社团与活动场所，与校史馆相邻。</t>
+          <t>柳湖东北侧大型教学楼，承担本科课堂教学。</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SVC-LOGI</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>后勤服务楼</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>服务配套</t>
+          <t>大学生活动中心</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>活动/报告厅</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -782,28 +782,28 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>9.17</v>
+        <v>36.39</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>121.84</v>
+        <v>116.15</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>20.89</v>
+        <v>25.32</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>12.03</v>
+        <v>16.78</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>wave</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>后勤服务、配套办公，邻地面停车场。</t>
+          <t>柳湖西北流线型白色参数化建筑，起伏曲面+穿孔表皮，学生社团与活动场所。</t>
         </is>
       </c>
     </row>
@@ -815,17 +815,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>SVC-LOGI</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>图书馆</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>图书馆</t>
+          <t>后勤服务楼</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>服务配套</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -834,28 +834,28 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>77.84999999999999</v>
+        <v>6.63</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>127.54</v>
+        <v>119.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>18.36</v>
+        <v>22.79</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>22.79</v>
+        <v>14.56</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>u</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>约5万㎡，红色层叠盒体+玻璃幕墙，临柳湖，含自习区/研讨室/创客空间/视听室。</t>
+          <t>后勤服务、配套办公，U形组合，邻地面停车场。</t>
         </is>
       </c>
     </row>
@@ -867,17 +867,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>GATE-E</t>
+          <t>LIB</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>东门</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>校门</t>
+          <t>图书馆</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>图书馆</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -886,28 +886,28 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>140.83</v>
+        <v>78.48</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>127.54</v>
+        <v>128.17</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3.8</v>
+        <v>14.56</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>9.5</v>
+        <v>18.36</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>lib</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>校园东侧出入口，车辆主出入口，紧邻机动车环岛。</t>
+          <t>约5万㎡，国家优质工程；红褐色横向百叶+玻璃幕墙的大体量方块，西北带凹口，临柳湖，含自习/研讨/创客/视听空间。</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
           <t>校史馆</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>校史馆/展馆</t>
         </is>
@@ -941,13 +941,13 @@
         <v>39.87</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>135.45</v>
+        <v>132.61</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>14.56</v>
+        <v>13.93</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>13.93</v>
+        <v>13.29</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>3</v>
@@ -979,7 +979,7 @@
           <t>紫竹餐厅（食堂）</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>食堂</t>
         </is>
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>22.46</v>
+        <v>19.93</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>135.77</v>
+        <v>133.87</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11.39</v>
+        <v>10.13</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>16.46</v>
+        <v>13.29</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>樱花苑3号楼北侧，含紫竹一~四食堂及民族食堂，约3900座。</t>
+          <t>樱花苑3号楼北侧，含紫竹一~四食堂及民族食堂，约3900座；红砖立面+竖向长条窗。</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
           <t>西门</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>校门</t>
         </is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>5.37</v>
+        <v>4.1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>137.04</v>
+        <v>134.5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>4.43</v>
+        <v>3.8</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>8.859999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1</v>
@@ -1083,7 +1083,7 @@
           <t>实验楼H</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>161.41</v>
+        <v>157.29</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>36.72</v>
+        <v>21.21</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4.75</v>
+        <v>6.96</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>5</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>东南科研实验群北排（编号按2021官方图，待与现状核对）。</t>
+          <t>北院北横档（北实验楼）。</t>
         </is>
       </c>
     </row>
@@ -1127,15 +1127,15 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>LAB-G</t>
+          <t>LAB-TECH</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>实验楼G</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
+          <t>科技创新楼</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1146,16 +1146,16 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>110.45</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>166.16</v>
+        <v>157.29</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>8.859999999999999</v>
+        <v>4.75</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>17.72</v>
+        <v>36.08</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>5</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>东南科研实验群东翼（编号待核对）。</t>
+          <t>实验群西翼（南北贯通），或为科技创新研究院。</t>
         </is>
       </c>
     </row>
@@ -1179,15 +1179,15 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>LAB-TECH</t>
+          <t>LAB-G</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>科技创新楼</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
+          <t>实验楼G</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1198,16 +1198,16 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>104.75</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>167.74</v>
+        <v>157.29</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>6.33</v>
+        <v>5.38</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>27.22</v>
+        <v>39.25</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>5</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>实验群西翼竖楼（名称待核对，或为科技创新研究院）。</t>
+          <t>实验群东翼（南北贯通，临东门）。</t>
         </is>
       </c>
     </row>
@@ -1231,17 +1231,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>LAB-F</t>
+          <t>GATE-E</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>实验楼F</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>实验/科研楼</t>
+          <t>东门</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>校门</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1250,19 +1250,19 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>88.93000000000001</v>
+        <v>114.88</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>169.32</v>
+        <v>165.52</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>21.52</v>
+        <v>3.8</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4.75</v>
+        <v>6.96</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>东南科研实验群。</t>
+          <t>校园东侧出入口，车辆主出入口，紧邻机动车环岛。</t>
         </is>
       </c>
     </row>
@@ -1283,15 +1283,15 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>LAB-E</t>
+          <t>LAB-F</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>实验楼E</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
+          <t>实验楼F</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1302,16 +1302,16 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>88.93000000000001</v>
+        <v>89.56</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>179.77</v>
+        <v>169.95</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>21.52</v>
+        <v>15.19</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>4.75</v>
+        <v>6.96</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>5</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>东南科研实验群。</t>
+          <t>北院南横档。</t>
         </is>
       </c>
     </row>
@@ -1335,15 +1335,15 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LAB-D</t>
+          <t>LAB-E</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>实验楼D</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
+          <t>实验楼E</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1354,16 +1354,16 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>108.55</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>183.56</v>
+        <v>177.55</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.13</v>
+        <v>21.21</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>12.66</v>
+        <v>6.96</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>5</v>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>科研实验群东南翼（编号待核对）。</t>
+          <t>南院北横档。</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
           <t>实验楼C</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>88.93000000000001</v>
+        <v>89.56</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>190.21</v>
+        <v>187.05</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>19.62</v>
+        <v>15.19</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4.75</v>
+        <v>6.33</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>5</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>东南科研实验群。</t>
+          <t>南院南横档。</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
           <t>第一教学楼</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>教学楼</t>
         </is>
@@ -1458,16 +1458,16 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>61.07</v>
+        <v>57.28</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>199.39</v>
+        <v>197.17</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>38.61</v>
+        <v>42.41</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15.83</v>
+        <v>18.99</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>5</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>弧形围合主教学楼，130间智慧教室，中央架空门廊；分A座(东)、B座(西)。</t>
+          <t>开口朝北的弧形围合主教学楼（凸面朝南），红褐色竖向格栅+白色平顶，中央架空门廊；130间智慧教室，分A座(东)、B座(西)。</t>
         </is>
       </c>
     </row>
@@ -1491,17 +1491,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FIELD-SW</t>
+          <t>GYM</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>操场（西南田径场）</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>室外运动场</t>
+          <t>体育馆</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>体育馆</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1510,28 +1510,28 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>7.27</v>
+        <v>48.41</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>199.71</v>
+        <v>219.01</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>36.72</v>
+        <v>25.32</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45.58</v>
+        <v>26.27</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>ellipse</t>
+          <t>gym</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>樱花苑南侧、体育馆西侧，标准足球场+环形跑道（风雨操场）。</t>
+          <t>矩形大跨综合体育馆，灰色大挑檐平屋顶+红墙+蓝色玻璃幕墙，临柳湖，含篮球/羽毛球/游泳等14个训练馆。</t>
         </is>
       </c>
     </row>
@@ -1543,17 +1543,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>GYM</t>
+          <t>GATE-S</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>体育馆</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>体育馆</t>
+          <t>主校门（南门）</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>校门</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1562,78 +1562,26 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45.88</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>220.6</v>
+        <v>254.15</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>29.12</v>
+        <v>12.66</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>25.32</v>
+        <v>5.06</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>ellipse</t>
+          <t>rect</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>椭圆船形综合体育馆，含篮球/羽毛球/网球/乒乓球等14个训练馆。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>GATE-S</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>主校门（南门）</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>校门</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>70.56999999999999</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>252.25</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>rect</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>学校正门、行人主出入口，校名石与『南涧路29号』标识，中轴礼仪序列起点。</t>
         </is>
@@ -1704,10 +1652,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46.83</v>
+        <v>45.25</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11.06</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="3">
@@ -1773,10 +1721,10 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>58.86</v>
+        <v>52.21</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>136.09</v>
+        <v>133.87</v>
       </c>
     </row>
     <row r="6">
@@ -1796,10 +1744,10 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>52.53</v>
+        <v>46.51</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>193.06</v>
+        <v>204.14</v>
       </c>
     </row>
     <row r="7">
@@ -1819,10 +1767,10 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>64.87</v>
+        <v>66.77</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>150.96</v>
+        <v>204.14</v>
       </c>
     </row>
     <row r="8">
@@ -2008,7 +1956,7 @@
       <c r="B2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>#C0392B</t>
         </is>
@@ -2023,7 +1971,7 @@
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>#C0392B</t>
         </is>
@@ -2038,7 +1986,7 @@
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>#A93226</t>
         </is>
@@ -2051,9 +1999,9 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>#B9772B</t>
         </is>
@@ -2068,7 +2016,7 @@
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>#9E4A30</t>
         </is>
@@ -2083,7 +2031,7 @@
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>#D35400</t>
         </is>
@@ -2098,7 +2046,7 @@
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>#CB4335</t>
         </is>
@@ -2113,7 +2061,7 @@
       <c r="B9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>#5D6D7E</t>
         </is>
@@ -2143,7 +2091,7 @@
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>#2E86C1</t>
         </is>

--- a/02_地图工程/建筑点位台账.xlsx
+++ b/02_地图工程/建筑点位台账.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CB4335"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAD7A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C0392B"/>
       </patternFill>
     </fill>
@@ -72,12 +82,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009E4A30"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CB4335"/>
+        <fgColor rgb="00B35035"/>
       </patternFill>
     </fill>
     <fill>
@@ -117,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -153,6 +158,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -520,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -664,7 +672,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>泰瑞楼（工程训练中心）</t>
+          <t>工程训练中心（泰瑞楼）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -711,38 +719,38 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TEACH-2</t>
+          <t>CAN-YULAN</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>第二教学楼</t>
+          <t>玉兰食堂（玉兰餐厅）</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>教学楼</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
+          <t>食堂</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>在建</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>61.07</v>
+        <v>40.18</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>108.23</v>
+        <v>104.12</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>27.22</v>
+        <v>14.24</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>23.74</v>
+        <v>10.76</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -751,7 +759,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>柳湖东北侧大型教学楼，承担本科课堂教学。</t>
+          <t>大学生活动中心北侧、景观渠西侧，官方图标注（在建）的玉兰餐厅，含玉兰二食堂。</t>
         </is>
       </c>
     </row>
@@ -763,17 +771,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>TEACH-2</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>大学生活动中心</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>活动/报告厅</t>
+          <t>第二教学楼</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>教学楼</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -782,28 +790,28 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>36.39</v>
+        <v>61.07</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>116.15</v>
+        <v>108.23</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>25.32</v>
+        <v>27.22</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>16.78</v>
+        <v>23.74</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>wave</t>
+          <t>rect</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>柳湖西北流线型白色参数化建筑，起伏曲面+穿孔表皮，学生社团与活动场所。</t>
+          <t>柳湖东北侧大型教学楼，承担本科课堂教学。</t>
         </is>
       </c>
     </row>
@@ -815,17 +823,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SVC-LOGI</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>后勤服务楼</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>服务配套</t>
+          <t>大学生活动中心</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>活动/报告厅</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -834,28 +842,28 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>6.63</v>
+        <v>36.39</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>119.63</v>
+        <v>116.15</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>22.79</v>
+        <v>25.32</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>14.56</v>
+        <v>16.78</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>wave</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>后勤服务、配套办公，U形组合，邻地面停车场。</t>
+          <t>柳湖西北流线型白色参数化建筑，起伏曲面+穿孔表皮，学生社团与活动场所。</t>
         </is>
       </c>
     </row>
@@ -875,7 +883,7 @@
           <t>图书馆</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>图书馆</t>
         </is>
@@ -919,17 +927,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>MUSEUM-HISTORY</t>
+          <t>CAN-ZIZHU</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>校史馆</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>校史馆/展馆</t>
+          <t>紫竹食堂（紫竹餐厅）</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>食堂</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -938,13 +946,13 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>39.87</v>
+        <v>19.93</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>132.61</v>
+        <v>133.87</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>13.93</v>
+        <v>10.13</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>13.29</v>
@@ -954,12 +962,12 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>ellipse</t>
+          <t>rect</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>柳湖沿畔圆形红棕展馆（2025年11月竣工，约2700㎡），与大学生活动中心相邻、临柳湖；校史陈列、研究与展览的校园文化空间。</t>
+          <t>樱花苑3号楼北侧，含紫竹一~四食堂及民族食堂，约3900座；红砖立面+竖向长条窗。</t>
         </is>
       </c>
     </row>
@@ -971,17 +979,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CAN-ZIZHU</t>
+          <t>GATE-W</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>紫竹餐厅（食堂）</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>食堂</t>
+          <t>西门</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>校门</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -990,19 +998,19 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>19.93</v>
+        <v>4.1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>133.87</v>
+        <v>134.5</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10.13</v>
+        <v>3.8</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>13.29</v>
+        <v>7.6</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1011,7 +1019,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>樱花苑3号楼北侧，含紫竹一~四食堂及民族食堂，约3900座；红砖立面+竖向长条窗。</t>
+          <t>校园西侧出入口，邻后勤服务楼与地面停车场，樱花苑生活片区主要人行入口。</t>
         </is>
       </c>
     </row>
@@ -1023,38 +1031,38 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>GATE-W</t>
+          <t>WENLI</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>西门</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>校门</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>已建</t>
+          <t>文理楼（文科楼）</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>学院楼</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>在建</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>4.1</v>
+        <v>104.75</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>134.5</v>
+        <v>138.3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3.8</v>
+        <v>13.29</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7.6</v>
+        <v>14.56</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1063,7 +1071,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>校园西侧出入口，邻后勤服务楼与地面停车场，樱花苑生活片区主要人行入口。</t>
+          <t>东门内北侧，官方平面图名『文科楼（在建）』，文理学科教学用房。</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1091,7 @@
           <t>实验楼H</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1135,7 +1143,7 @@
           <t>科技创新楼</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1187,7 +1195,7 @@
           <t>实验楼G</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1239,7 +1247,7 @@
           <t>东门</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>校门</t>
         </is>
@@ -1291,7 +1299,7 @@
           <t>实验楼F</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1343,7 +1351,7 @@
           <t>实验楼E</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1395,7 +1403,7 @@
           <t>实验楼C</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1439,17 +1447,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>TEACH-1</t>
+          <t>FIELD-W</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>第一教学楼</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>教学楼</t>
+          <t>风雨操场（西田径场）</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>室外运动场</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1458,28 +1466,28 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>57.28</v>
+        <v>13.91</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>197.17</v>
+        <v>192.11</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>42.41</v>
+        <v>29.75</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>18.99</v>
+        <v>36.72</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>arc</t>
+          <t>ellipse</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>开口朝北的弧形围合主教学楼（凸面朝南），红褐色竖向格栅+白色平顶，中央架空门廊；130间智慧教室，分A座(东)、B座(西)。</t>
+          <t>校园西南侧西田径场（用户标注『风雨操场』），足球场+环形跑道，西侧/北侧蓝色看台，东邻篮球场与南湖，东南邻体育馆。</t>
         </is>
       </c>
     </row>
@@ -1491,17 +1499,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>GYM</t>
+          <t>TEACH-1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>体育馆</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>体育馆</t>
+          <t>第一教学楼</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>教学楼</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1510,28 +1518,28 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>48.41</v>
+        <v>57.28</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>219.01</v>
+        <v>197.17</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>25.32</v>
+        <v>42.41</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>26.27</v>
+        <v>18.99</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>gym</t>
+          <t>arc</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>矩形大跨综合体育馆，灰色大挑檐平屋顶+红墙+蓝色玻璃幕墙，临柳湖，含篮球/羽毛球/游泳等14个训练馆。</t>
+          <t>开口朝北的弧形围合主教学楼（凸面朝南），红褐色竖向格栅+白色平顶，中央架空门廊；130间智慧教室，分A座(东)、B座(西)。</t>
         </is>
       </c>
     </row>
@@ -1543,45 +1551,97 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>GYM</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>体育馆</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>体育馆</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>已建</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>48.41</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>219.01</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>gym</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>矩形大跨综合体育馆，灰色大挑檐平屋顶+红墙+蓝色玻璃幕墙，临柳湖，含篮球/羽毛球/游泳等14个训练馆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>GATE-S</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>主校门（南门）</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>校门</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>已建</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F21" s="2" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G21" s="2" t="n">
         <v>254.15</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H21" s="2" t="n">
         <v>12.66</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I21" s="2" t="n">
         <v>5.06</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>rect</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>学校正门、行人主出入口，校名石与『南涧路29号』标识，中轴礼仪序列起点。</t>
         </is>
@@ -1956,7 +2016,7 @@
       <c r="B2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>#C0392B</t>
         </is>
@@ -1971,7 +2031,7 @@
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>#C0392B</t>
         </is>
@@ -1986,7 +2046,7 @@
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>#A93226</t>
         </is>
@@ -2001,7 +2061,7 @@
       <c r="B5" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>#B9772B</t>
         </is>
@@ -2010,15 +2070,15 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>校史馆/展馆</t>
+          <t>学院楼</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>#9E4A30</t>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>#B35035</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2091,7 @@
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>#D35400</t>
         </is>
@@ -2044,9 +2104,9 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>#CB4335</t>
         </is>
@@ -2059,7 +2119,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -2076,7 +2136,7 @@
       <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>#922B21</t>
         </is>
@@ -2089,7 +2149,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>

--- a/02_地图工程/建筑点位台账.xlsx
+++ b/02_地图工程/建筑点位台账.xlsx
@@ -738,28 +738,28 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>40.18</v>
+        <v>40.82</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>104.12</v>
+        <v>102.22</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>14.24</v>
+        <v>13.29</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>10.76</v>
+        <v>13.29</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>poly</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>大学生活动中心北侧、景观渠西侧，官方图标注（在建）的玉兰餐厅，含玉兰二食堂。</t>
+          <t>大学生活动中心北侧、景观渠西侧，官方图标注（在建）的玉兰餐厅，主体方块+北缘小凸体，含玉兰二食堂。</t>
         </is>
       </c>
     </row>
@@ -799,19 +799,19 @@
         <v>27.22</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>23.74</v>
+        <v>20.57</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>5</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>poly</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>柳湖东北侧大型教学楼，承担本科课堂教学。</t>
+          <t>柳湖东北侧大型教学楼（大矩形+南缘锯齿/退台），承担本科课堂教学。</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>柳湖西北流线型白色参数化建筑，起伏曲面+穿孔表皮，学生社团与活动场所。</t>
+          <t>柳湖西北白色参数化建筑：西侧一座小三角楔块+东侧大不规则主体（官方图两体块），起伏曲面+穿孔表皮，学生社团与活动场所。</t>
         </is>
       </c>
     </row>
@@ -900,22 +900,22 @@
         <v>128.17</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>14.56</v>
+        <v>18.67</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>18.36</v>
+        <v>20.89</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>lib</t>
+          <t>libL</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>约5万㎡，国家优质工程；红褐色横向百叶+玻璃幕墙的大体量方块，西北带凹口，临柳湖，含自习/研讨/创客/视听空间。</t>
+          <t>约5万㎡，国家优质工程；主体大方块+东侧竖向百叶塔楼（北半部相连，L形），红褐色横百叶+玻璃幕墙，临柳湖，含自习/研讨/创客/视听空间。</t>
         </is>
       </c>
     </row>
@@ -952,22 +952,22 @@
         <v>133.87</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.13</v>
+        <v>9.5</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>13.29</v>
+        <v>22.79</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>poly</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>樱花苑3号楼北侧，含紫竹一~四食堂及民族食堂，约3900座；红砖立面+竖向长条窗。</t>
+          <t>樱花苑3号楼北侧，竖长楼体（北缘双凸），含紫竹一~四食堂及民族食堂，约3900座；红砖立面+竖向长条窗。</t>
         </is>
       </c>
     </row>
@@ -1050,28 +1050,28 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>104.75</v>
+        <v>99.06</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>138.3</v>
+        <v>134.5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>13.29</v>
+        <v>18.36</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>14.56</v>
+        <v>22.16</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>5</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>poly</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>东门内北侧，官方平面图名『文科楼（在建）』，文理学科教学用房。</t>
+          <t>东门内北侧，官方平面图名『文科楼（在建）』，三条西向横档+东侧竖档的3字（E）形竖长楼，文理学科教学用房。</t>
         </is>
       </c>
     </row>
@@ -1518,28 +1518,28 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>57.28</v>
+        <v>56.64</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>197.17</v>
+        <v>196.54</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>42.41</v>
+        <v>43.68</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>18.99</v>
+        <v>20.26</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>5</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>arc</t>
+          <t>crescent</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>开口朝北的弧形围合主教学楼（凸面朝南），红褐色竖向格栅+白色平顶，中央架空门廊；130间智慧教室，分A座(东)、B座(西)。</t>
+          <t>弯月形（凸面朝南）主教学楼，中央为通透大拱门、左右两座弧形翼（A座东/B座西），顶部连廊相接；红褐色竖向格栅+白色平顶，130间智慧教室。</t>
         </is>
       </c>
     </row>
@@ -1570,28 +1570,28 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>48.41</v>
+        <v>49.92</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>219.01</v>
+        <v>223.02</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>25.32</v>
+        <v>21.04</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>26.27</v>
+        <v>19.21</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>gym</t>
+          <t>capsule</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>矩形大跨综合体育馆，灰色大挑檐平屋顶+红墙+蓝色玻璃幕墙，临柳湖，含篮球/羽毛球/游泳等14个训练馆。</t>
+          <t>主校门西侧倾斜胶囊形（圆角矩形大跨）综合体育馆，长轴沿西北-东南，灰色大挑檐平顶+红墙+蓝玻璃幕墙，含篮球/羽毛球/游泳等14个训练馆。</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
         <v>45.25</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>16.13</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="3">

--- a/02_地图工程/建筑点位台账.xlsx
+++ b/02_地图工程/建筑点位台账.xlsx
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>83.55</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30.69</v>
+        <v>33.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>23.42</v>
+        <v>14.56</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>30.39</v>
+        <v>29.75</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
@@ -655,7 +655,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>校园东北侧东田径场（用户标注『北操场』），标准足球场+环形跑道，南北长轴，北邻游泳馆/篮球馆。</t>
+          <t>校园东北侧东田径场（用户标注『北操场』），标准足球场+环形跑道（跑道形，南北长轴），北邻游泳馆/篮球馆。</t>
         </is>
       </c>
     </row>
@@ -1466,16 +1466,16 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>13.91</v>
+        <v>12.33</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>192.11</v>
+        <v>191.16</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>29.75</v>
+        <v>16.46</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>36.72</v>
+        <v>29.12</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>校园西南侧西田径场（用户标注『风雨操场』），足球场+环形跑道，西侧/北侧蓝色看台，东邻篮球场与南湖，东南邻体育馆。</t>
+          <t>校园西南侧西田径场（用户标注『风雨操场』），跑道形足球场+环形跑道（南北长轴），东侧篮球场/游泳馆，东邻南湖，东南邻体育馆。</t>
         </is>
       </c>
     </row>
@@ -1570,28 +1570,28 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>49.92</v>
+        <v>51.25</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>223.02</v>
+        <v>224.71</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>21.04</v>
+        <v>19.64</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>19.21</v>
+        <v>19.63</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>capsule</t>
+          <t>gymbox</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>主校门西侧倾斜胶囊形（圆角矩形大跨）综合体育馆，长轴沿西北-东南，灰色大挑檐平顶+红墙+蓝玻璃幕墙，含篮球/羽毛球/游泳等14个训练馆。</t>
+          <t>主校门西北侧跑道形（圆角矩形）大跨综合体育馆，长轴东偏北约45°，灰色大挑檐平顶+红砖方柱+朝东南蓝玻璃幕墙，含篮球/羽毛球/游泳等14个训练馆。</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>45.25</v>
+        <v>41.45</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>15.5</v>

--- a/02_地图工程/建筑点位台账.xlsx
+++ b/02_地图工程/建筑点位台账.xlsx
@@ -738,16 +738,16 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>40.82</v>
+        <v>39.87</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>102.22</v>
+        <v>107.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>13.29</v>
+        <v>10.44</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>13.29</v>
+        <v>9.18</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>3</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>大学生活动中心北侧、景观渠西侧，官方图标注（在建）的玉兰餐厅，主体方块+北缘小凸体，含玉兰二食堂。</t>
+          <t>大学生活动中心北侧、景观渠西侧，官方图标注（在建）的玉兰餐厅，蓝色方块+西侧小突出翼+南缘弧，含玉兰二食堂。</t>
         </is>
       </c>
     </row>
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>61.07</v>
+        <v>62.66</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>108.23</v>
+        <v>112.03</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>27.22</v>
+        <v>19.94</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>20.57</v>
+        <v>18.36</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>5</v>
@@ -811,7 +811,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>柳湖东北侧大型教学楼（大矩形+南缘锯齿/退台），承担本科课堂教学。</t>
+          <t>柳湖东北侧大型教学楼：大矩形主体沿斜向宏德大道，东缘被斜路切出斜边、南缘带退台，承担本科课堂教学。</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>wave</t>
+          <t>act</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -894,28 +894,28 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>78.48</v>
+        <v>80.06</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>128.17</v>
+        <v>130.39</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>18.67</v>
+        <v>14.88</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>20.89</v>
+        <v>15.83</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>libL</t>
+          <t>poly</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>约5万㎡，国家优质工程；主体大方块+东侧竖向百叶塔楼（北半部相连，L形），红褐色横百叶+玻璃幕墙，临柳湖，含自习/研讨/创客/视听空间。</t>
+          <t>约5万㎡，国家优质工程；主体大方块（西北角U形凹口）+东侧竖向百叶附楼，红褐色横百叶+玻璃幕墙，临柳湖，含自习/研讨/创客/视听空间。</t>
         </is>
       </c>
     </row>
@@ -927,17 +927,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CAN-ZIZHU</t>
+          <t>GATE-W</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>紫竹食堂（紫竹餐厅）</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>食堂</t>
+          <t>西门</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>校门</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -946,28 +946,28 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>19.93</v>
+        <v>4.1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>133.87</v>
+        <v>134.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9.5</v>
+        <v>3.8</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22.79</v>
+        <v>7.6</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>poly</t>
+          <t>rect</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>樱花苑3号楼北侧，竖长楼体（北缘双凸），含紫竹一~四食堂及民族食堂，约3900座；红砖立面+竖向长条窗。</t>
+          <t>校园西侧出入口，邻后勤服务楼与地面停车场，樱花苑生活片区主要人行入口。</t>
         </is>
       </c>
     </row>
@@ -979,17 +979,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>GATE-W</t>
+          <t>CAN-ZIZHU</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>西门</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>校门</t>
+          <t>紫竹食堂（紫竹餐厅）</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>食堂</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -998,28 +998,28 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.1</v>
+        <v>24.04</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>134.5</v>
+        <v>136.72</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>3.8</v>
+        <v>8.23</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>7.6</v>
+        <v>12.03</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>poly</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>校园西侧出入口，邻后勤服务楼与地面停车场，樱花苑生活片区主要人行入口。</t>
+          <t>西门内粉色竖长楼体，北缘双塔楼（两凸体间凹口），含紫竹一~四食堂及民族食堂，约3900座；红砖立面+竖向长条窗。</t>
         </is>
       </c>
     </row>
@@ -1053,13 +1053,13 @@
         <v>99.06</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>134.5</v>
+        <v>138.94</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>18.36</v>
+        <v>15.83</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>22.16</v>
+        <v>14.56</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>5</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>东门内北侧，官方平面图名『文科楼（在建）』，三条西向横档+东侧竖档的3字（E）形竖长楼，文理学科教学用房。</t>
+          <t>东门内北侧，官方平面图名『文科楼（在建）』，蓝色玻璃幕墙大方块（水平分段），文理学科教学用房。</t>
         </is>
       </c>
     </row>
@@ -1518,16 +1518,16 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>56.64</v>
+        <v>56.33</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>196.54</v>
+        <v>197.81</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>43.68</v>
+        <v>44.31</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>20.26</v>
+        <v>20.89</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>5</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>弯月形（凸面朝南）主教学楼，中央为通透大拱门、左右两座弧形翼（A座东/B座西），顶部连廊相接；红褐色竖向格栅+白色平顶，130间智慧教室。</t>
+          <t>开口朝南的马蹄形（U形）主教学楼：北侧中央为南北向玻璃主楼，东西两座弧形翼（A座西/B座东）由北连廊相接并向南围合出庭院；红褐色竖向格栅+白色平顶，130间智慧教室。</t>
         </is>
       </c>
     </row>

--- a/02_地图工程/建筑点位台账.xlsx
+++ b/02_地图工程/建筑点位台账.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -58,11 +58,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00CB4335"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAD7A0"/>
       </patternFill>
     </fill>
     <fill>
@@ -122,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -158,9 +153,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -707,7 +699,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>东北侧工程训练中心『泰瑞楼』（泰瑞机器冠名捐赠），工程实践教学场地。</t>
+          <t>东北侧工程训练中心『泰瑞楼』（泰瑞机器冠名捐赠），红棕+浅灰板立面、横向条窗，转角内凹二层高玻璃入口，工程实践教学场地。</t>
         </is>
       </c>
     </row>
@@ -732,34 +724,34 @@
           <t>食堂</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>在建</t>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>已建</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>39.87</v>
+        <v>41.45</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>107.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.44</v>
+        <v>7.6</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>9.18</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>poly</t>
+          <t>yulan</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>大学生活动中心北侧、景观渠西侧，官方图标注（在建）的玉兰餐厅，蓝色方块+西侧小突出翼+南缘弧，含玉兰二食堂。</t>
+          <t>红砖盒形交错层叠食堂，室外大台阶直通二层、二层架空挑檐白柱、上层一条蓝玻带，含玉兰一/二食堂。</t>
         </is>
       </c>
     </row>
@@ -779,7 +771,7 @@
           <t>第二教学楼</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>教学楼</t>
         </is>
@@ -790,16 +782,16 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>62.66</v>
+        <v>62.97</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>112.03</v>
+        <v>111.72</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>19.94</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>18.36</v>
+        <v>17.41</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>5</v>
@@ -811,7 +803,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>柳湖东北侧大型教学楼：大矩形主体沿斜向宏德大道，东缘被斜路切出斜边、南缘带退台，承担本科课堂教学。</t>
+          <t>柳湖东北侧红砖多体块围合院落群（约5-6体块、2-3内院+连廊，局部绿色屋顶，南门廊），承担本科课堂教学。</t>
         </is>
       </c>
     </row>
@@ -831,7 +823,7 @@
           <t>大学生活动中心</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>活动/报告厅</t>
         </is>
@@ -842,16 +834,16 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>36.39</v>
+        <v>38.6</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>116.15</v>
+        <v>120.58</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>25.32</v>
+        <v>16.78</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>16.78</v>
+        <v>11.08</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>3</v>
@@ -863,7 +855,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>柳湖西北白色参数化建筑：西侧一座小三角楔块+东侧大不规则主体（官方图两体块），起伏曲面+穿孔表皮，学生社团与活动场所。</t>
+          <t>单一白色菱形穿孔表皮体量（两翼南连、北缘V形凹口），南檐口波浪下凹，白平顶+矩形天窗，含剧场/社团/展厅。</t>
         </is>
       </c>
     </row>
@@ -883,7 +875,7 @@
           <t>图书馆</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>图书馆</t>
         </is>
@@ -894,16 +886,16 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>80.06</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>130.39</v>
+        <v>131.34</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>14.88</v>
+        <v>17.72</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15.83</v>
+        <v>13.61</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>6</v>
@@ -915,7 +907,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>约5万㎡，国家优质工程；主体大方块（西北角U形凹口）+东侧竖向百叶附楼，红褐色横百叶+玻璃幕墙，临柳湖，含自习/研讨/创客/视听空间。</t>
+          <t>约5万㎡，国家优质工程；连续折线单一体量（东侧百叶带与主体连体）+中央三角形玻璃采光中庭+弧形转角，红褐色横百叶+玻璃幕墙，临柳湖。</t>
         </is>
       </c>
     </row>
@@ -935,7 +927,7 @@
           <t>西门</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>校门</t>
         </is>
@@ -967,7 +959,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>校园西侧出入口，邻后勤服务楼与地面停车场，樱花苑生活片区主要人行入口。</t>
+          <t>深灰青砖马头墙三退台高门柱（圆形校徽+竖排校名+中式瓦檐）+矮灰砖玻璃岗亭+黑色电动伸缩门。</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1031,30 @@
           <t>文理楼（文科楼）</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>学院楼</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>在建</t>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>已建</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>99.06</v>
+        <v>104.75</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>138.94</v>
+        <v>141.47</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>15.83</v>
+        <v>11.39</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>14.56</v>
+        <v>12.98</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1071,7 +1063,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>东门内北侧，官方平面图名『文科楼（在建）』，蓝色玻璃幕墙大方块（水平分段），文理学科教学用房。</t>
+          <t>周恺设计红砖围合院落（C形，朝西开口内院）4层，水平条窗+局部镂空砖格栅、东北退台，文理学科教学用房。</t>
         </is>
       </c>
     </row>
@@ -1083,15 +1075,15 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>LAB-H</t>
+          <t>LAB-TECH</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>实验楼H</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
+          <t>实验楼A（西翼）</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1102,16 +1094,16 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>85.76000000000001</v>
+        <v>86.39</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>157.29</v>
+        <v>159.83</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>21.21</v>
+        <v>4.43</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6.96</v>
+        <v>33.55</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>5</v>
@@ -1123,7 +1115,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>北院北横档（北实验楼）。</t>
+          <t>实验群西翼（南北贯通两进院），红褐陶土下部+浅灰板带上部、密排竖窗，中段内凹Π形玻璃门厅，实景标牌『实验楼A』。</t>
         </is>
       </c>
     </row>
@@ -1135,15 +1127,15 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>LAB-TECH</t>
+          <t>LAB-G</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>科技创新楼</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
+          <t>实验楼G（东翼）</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1154,16 +1146,16 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>85.76000000000001</v>
+        <v>107.6</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>157.29</v>
+        <v>159.83</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>4.75</v>
+        <v>3.48</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>36.08</v>
+        <v>34.18</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>5</v>
@@ -1175,7 +1167,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>实验群西翼（南北贯通），或为科技创新研究院。</t>
+          <t>实验群东翼（南北贯通、比西翼更长，临东门环岛）。</t>
         </is>
       </c>
     </row>
@@ -1187,15 +1179,15 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>LAB-G</t>
+          <t>LAB-H</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>实验楼G</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
+          <t>实验楼H</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1206,16 +1198,16 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>104.75</v>
+        <v>90.83</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>157.29</v>
+        <v>161.72</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>5.38</v>
+        <v>16.78</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>39.25</v>
+        <v>3.8</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>5</v>
@@ -1227,7 +1219,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>实验群东翼（南北贯通，临东门）。</t>
+          <t>北院北横档（北实验楼），红褐陶土+浅灰板带。</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1239,7 @@
           <t>东门</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>校门</t>
         </is>
@@ -1279,7 +1271,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>校园东侧出入口，车辆主出入口，紧邻机动车环岛。</t>
+          <t>校园东侧出入口，车辆主出入口，1层简易道闸门房，门内西侧机动车环岛。</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1291,7 @@
           <t>实验楼F</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1310,16 +1302,16 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>89.56</v>
+        <v>90.83</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>169.95</v>
+        <v>171.85</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>15.19</v>
+        <v>16.78</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>6.96</v>
+        <v>5.06</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>5</v>
@@ -1331,7 +1323,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>北院南横档。</t>
+          <t>北院南横档（与南院北横档E紧贴分隔两院）。</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1343,7 @@
           <t>实验楼E</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1362,16 +1354,16 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>85.76000000000001</v>
+        <v>90.83</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>177.55</v>
+        <v>180.08</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>21.21</v>
+        <v>16.78</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>6.96</v>
+        <v>4.43</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>5</v>
@@ -1403,7 +1395,7 @@
           <t>实验楼C</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>实验/科研楼</t>
         </is>
@@ -1414,16 +1406,16 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>89.56</v>
+        <v>90.83</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>187.05</v>
+        <v>190.21</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>15.19</v>
+        <v>16.78</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>6.33</v>
+        <v>3.8</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>5</v>
@@ -1507,7 +1499,7 @@
           <t>第一教学楼</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>教学楼</t>
         </is>
@@ -1559,7 +1551,7 @@
           <t>体育馆</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>体育馆</t>
         </is>
@@ -1611,7 +1603,7 @@
           <t>主校门（南门）</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>校门</t>
         </is>
@@ -1643,7 +1635,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>学校正门、行人主出入口，校名石与『南涧路29号』标识，中轴礼仪序列起点。</t>
+          <t>学校正门、敞开式无门楼，横卧校名石（红字）+石后旗杆+两侧灰色矮岗亭，中轴礼仪序列起点。</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2008,7 @@
       <c r="B2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>#C0392B</t>
         </is>
@@ -2031,7 +2023,7 @@
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>#C0392B</t>
         </is>
@@ -2046,7 +2038,7 @@
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>#A93226</t>
         </is>
@@ -2061,7 +2053,7 @@
       <c r="B5" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>#B9772B</t>
         </is>
@@ -2076,7 +2068,7 @@
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>#B35035</t>
         </is>
@@ -2091,7 +2083,7 @@
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>#D35400</t>
         </is>
@@ -2136,7 +2128,7 @@
       <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>#922B21</t>
         </is>
